--- a/InputData/hydgn/HPEbP/Hydgn Production Eff by Pathway.xlsx
+++ b/InputData/hydgn/HPEbP/Hydgn Production Eff by Pathway.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\NH\hydgn\HPEbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\hydgn\HPEbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DEEC4F5-01FD-4E8F-8E99-D390D1A2ACBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177EA61C-757C-475C-B06D-DD0B50AFCBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="375" windowWidth="13680" windowHeight="17025" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="IEA Data" sheetId="3" r:id="rId2"/>
     <sheet name="HPEbP" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>HPEbP Hydrogen Production Efficiency by Pathway</t>
   </si>
@@ -176,7 +176,10 @@
     <t>Appendix D (biomass), Appendix H (natural gas), Appendix I (electrolysis), and Appendix J (coal)</t>
   </si>
   <si>
-    <t>New Hampshire</t>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -279,7 +282,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -561,24 +563,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="98.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="14">
-        <v>44811</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,57 +582,57 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>45</v>
       </c>
@@ -991,7 +987,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" customWidth="1"/>
@@ -1809,6 +1805,288 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="6">
+        <f>B2</f>
+        <v>0.67045454545454541</v>
+      </c>
+      <c r="C7" s="6">
+        <f t="shared" ref="C7:AI7" si="6">C2</f>
+        <v>0.6743453210151954</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.67825867548826535</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.682194739903489</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.68615364605099072</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.69013552648569809</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.69414051453178016</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.69816874428711162</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.70222035062776267</v>
+      </c>
+      <c r="K7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.70629546921251507</v>
+      </c>
+      <c r="L7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.71039423648740441</v>
+      </c>
+      <c r="M7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.71451678969028842</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.71866326685544257</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.72283380681818132</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.7253666557451437</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.72790837991234292</v>
+      </c>
+      <c r="R7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.73045901041910288</v>
+      </c>
+      <c r="S7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.73301857847372121</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.73558711539385124</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.73816465260688491</v>
+      </c>
+      <c r="V7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.74075122165033747</v>
+      </c>
+      <c r="W7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.74334685417223334</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.74595158193149347</v>
+      </c>
+      <c r="Y7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.74856543679832355</v>
+      </c>
+      <c r="Z7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.7511884507546045</v>
+      </c>
+      <c r="AA7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.75382065589428315</v>
+      </c>
+      <c r="AB7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.7564620844237655</v>
+      </c>
+      <c r="AC7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.75911276866231048</v>
+      </c>
+      <c r="AD7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.76177274104242554</v>
+      </c>
+      <c r="AE7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.76444203411026324</v>
+      </c>
+      <c r="AF7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.76712068052601967</v>
+      </c>
+      <c r="AG7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.76980871306433407</v>
+      </c>
+      <c r="AH7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.77250616461468979</v>
+      </c>
+      <c r="AI7" s="6">
+        <f t="shared" si="6"/>
+        <v>0.77521306818181679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="6">
+        <f>B3</f>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="C8" s="6">
+        <f t="shared" ref="C8:AI8" si="7">C3</f>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="H8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="L8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="S8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="V8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="X8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="Y8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="Z8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AA8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AB8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AC8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AD8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AE8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AF8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AG8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AH8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="AI8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.71951219512195119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
